--- a/data/trans_bre/P16A09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A09-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,13</t>
+          <t>-1,39; 4,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,89</t>
+          <t>-3,84; 0,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,08</t>
+          <t>-0,74; 2,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,63</t>
+          <t>0,68; 3,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,47; 262,91</t>
+          <t>-46,45; 289,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-88,07; 113,87</t>
+          <t>-89,54; 80,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,1; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,37; 824,83</t>
+          <t>15,99; 769,56</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,66</t>
+          <t>-0,65; 3,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,11</t>
+          <t>-1,11; 3,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,12</t>
+          <t>0,31; 2,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,65</t>
+          <t>0,84; 4,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,98; 632,9</t>
+          <t>-48,9; 702,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,73; 317,66</t>
+          <t>-54,13; 390,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,53; 684,59</t>
+          <t>20,98; 599,63</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 8,98</t>
+          <t>0,64; 9,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 5,22</t>
+          <t>-0,78; 5,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 7,98</t>
+          <t>0,28; 7,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 13,16</t>
+          <t>3,35; 12,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 452,6</t>
+          <t>2,94; 461,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,89; 360,11</t>
+          <t>-36,11; 375,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 2346,49</t>
+          <t>-27,14; 2039,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>108,9; 1891,6</t>
+          <t>124,72; 2121,6</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,44</t>
+          <t>-2,08; 1,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,25</t>
+          <t>-0,72; 2,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,11</t>
+          <t>-1,5; 1,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,22</t>
+          <t>-1,74; 1,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,64; 39,0</t>
+          <t>-40,5; 40,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,75; 129,28</t>
+          <t>-27,64; 121,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,85; 75,7</t>
+          <t>-59,36; 72,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,19; 54,62</t>
+          <t>-54,51; 57,81</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,86</t>
+          <t>-0,17; 5,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,83</t>
+          <t>2,38; 6,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,71</t>
+          <t>1,6; 5,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,95</t>
+          <t>2,26; 7,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 303,39</t>
+          <t>-8,85; 301,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,76; 489,26</t>
+          <t>65,07; 534,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,07; 389,87</t>
+          <t>42,52; 369,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,43; 416,17</t>
+          <t>66,55; 447,28</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,05</t>
+          <t>4,84; 7,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,92; 11,62</t>
+          <t>8,04; 11,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,2</t>
+          <t>4,27; 7,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,19; 8,83</t>
+          <t>6,21; 9,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,15</t>
+          <t>1,24; 3,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,66</t>
+          <t>2,72; 4,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,21</t>
+          <t>1,62; 3,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,19</t>
+          <t>2,34; 4,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,72; 124,2</t>
+          <t>35,55; 121,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>111,74; 269,03</t>
+          <t>109,57; 270,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100,6; 300,93</t>
+          <t>97,01; 305,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>107,5; 297,96</t>
+          <t>116,36; 309,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A09-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>2,08</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>222,41%</t>
+          <t>231,57%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,11</t>
+          <t>-1,36; 3,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,81</t>
+          <t>-3,51; 0,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,12</t>
+          <t>-0,75; 2,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,53</t>
+          <t>0,65; 3,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 289,48</t>
+          <t>-44,71; 256,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-89,54; 80,53</t>
+          <t>-90,47; 77,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-78,1; —</t>
+          <t>-100,0; 1303,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 769,56</t>
+          <t>17,53; 994,15</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>201,65%</t>
+          <t>197,16%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,42</t>
+          <t>-0,72; 3,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,42</t>
+          <t>-1,34; 2,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,86</t>
+          <t>0,28; 2,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,48</t>
+          <t>0,71; 4,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,9; 702,88</t>
+          <t>-60,57; 597,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,13; 390,31</t>
+          <t>-57,96; 262,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,98; 599,63</t>
+          <t>14,36; 721,35</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>442,66%</t>
+          <t>261,01%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 9,62</t>
+          <t>0,4; 8,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 5,32</t>
+          <t>-0,88; 5,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 7,35</t>
+          <t>0,45; 7,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 12,62</t>
+          <t>2,62; 11,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 461,47</t>
+          <t>1,11; 453,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 375,33</t>
+          <t>-46,84; 342,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 2039,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>124,72; 2121,6</t>
+          <t>80,96; 788,83</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-2,12%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,47</t>
+          <t>-2,18; 1,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,22</t>
+          <t>-0,85; 2,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,0</t>
+          <t>-1,41; 1,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,37</t>
+          <t>-0,6; 2,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,5; 40,05</t>
+          <t>-44,15; 42,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 121,23</t>
+          <t>-29,69; 138,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 72,22</t>
+          <t>-54,47; 71,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,51; 57,81</t>
+          <t>-19,3; 103,73</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,62</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>196,38%</t>
+          <t>227,92%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,08</t>
+          <t>-0,51; 4,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,98</t>
+          <t>2,11; 6,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,8</t>
+          <t>1,62; 5,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,25</t>
+          <t>3,26; 6,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 301,37</t>
+          <t>-12,19; 294,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,07; 534,79</t>
+          <t>53,67; 498,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,52; 369,36</t>
+          <t>40,65; 357,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>66,55; 447,28</t>
+          <t>102,49; 526,36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,43</t>
+          <t>7,5</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,84; 7,91</t>
+          <t>4,92; 7,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 11,78</t>
+          <t>7,99; 11,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,25</t>
+          <t>4,21; 7,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,1</t>
+          <t>6,07; 9,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>3,63</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>192,29%</t>
+          <t>195,51%</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,11</t>
+          <t>1,25; 3,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,68</t>
+          <t>2,84; 4,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1275,27 +1275,27 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,22</t>
+          <t>2,84; 4,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,55; 121,13</t>
+          <t>34,47; 120,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>109,57; 270,05</t>
+          <t>114,54; 283,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,01; 305,61</t>
+          <t>100,82; 304,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>116,36; 309,33</t>
+          <t>129,89; 280,36</t>
         </is>
       </c>
     </row>
